--- a/math121-schedule.xlsx
+++ b/math121-schedule.xlsx
@@ -742,6 +742,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -779,21 +794,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1155,7 +1155,7 @@
       <c r="C2" s="15">
         <v>46265</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="38" t="s">
         <v>46</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -1173,7 +1173,7 @@
         <f>C2+3</f>
         <v>46268</v>
       </c>
-      <c r="D3" s="51"/>
+      <c r="D3" s="38"/>
       <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
@@ -1242,7 +1242,7 @@
         <f t="shared" ref="C6:C35" si="2">C4+7</f>
         <v>46279</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="38" t="s">
         <v>49</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -1265,7 +1265,7 @@
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="D7" s="51"/>
+      <c r="D7" s="38"/>
       <c r="E7" s="6" t="s">
         <v>9</v>
       </c>
@@ -1287,7 +1287,7 @@
         <f t="shared" si="2"/>
         <v>46286</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="38" t="s">
         <v>50</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -1310,7 +1310,7 @@
         <f t="shared" si="2"/>
         <v>46289</v>
       </c>
-      <c r="D9" s="51"/>
+      <c r="D9" s="38"/>
       <c r="E9" s="6" t="s">
         <v>11</v>
       </c>
@@ -1349,12 +1349,12 @@
       <c r="C11" s="15">
         <v>46294</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
@@ -1388,7 +1388,7 @@
         <f>C10+7</f>
         <v>46300</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="38" t="s">
         <v>51</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -1409,7 +1409,7 @@
         <f t="shared" si="2"/>
         <v>46303</v>
       </c>
-      <c r="D14" s="51"/>
+      <c r="D14" s="38"/>
       <c r="E14" s="6" t="s">
         <v>15</v>
       </c>
@@ -1429,7 +1429,7 @@
         <f t="shared" si="2"/>
         <v>46307</v>
       </c>
-      <c r="D15" s="51" t="s">
+      <c r="D15" s="38" t="s">
         <v>52</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -1452,7 +1452,7 @@
         <f t="shared" si="2"/>
         <v>46310</v>
       </c>
-      <c r="D16" s="51"/>
+      <c r="D16" s="38"/>
       <c r="E16" s="6" t="s">
         <v>17</v>
       </c>
@@ -1488,7 +1488,7 @@
         <f t="shared" si="2"/>
         <v>46317</v>
       </c>
-      <c r="D18" s="51" t="s">
+      <c r="D18" s="38" t="s">
         <v>53</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -1511,7 +1511,7 @@
         <f t="shared" si="2"/>
         <v>46321</v>
       </c>
-      <c r="D19" s="51"/>
+      <c r="D19" s="38"/>
       <c r="E19" s="6" t="s">
         <v>19</v>
       </c>
@@ -1526,23 +1526,23 @@
       <c r="C20" s="15">
         <v>46322</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="D20" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="55"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="42"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <f>A18+1</f>
         <v>9</v>
       </c>
-      <c r="B21" s="38" t="str">
+      <c r="B21" s="43" t="str">
         <f>B18</f>
         <v>Thu</v>
       </c>
-      <c r="C21" s="40">
+      <c r="C21" s="45">
         <f>C18+7</f>
         <v>46324</v>
       </c>
@@ -1559,14 +1559,14 @@
     </row>
     <row r="22" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="42" t="s">
+      <c r="B22" s="44"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="44"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
@@ -1600,7 +1600,7 @@
         <f>C21+7</f>
         <v>46331</v>
       </c>
-      <c r="D24" s="51" t="s">
+      <c r="D24" s="38" t="s">
         <v>54</v>
       </c>
       <c r="E24" s="6" t="s">
@@ -1621,7 +1621,7 @@
         <f t="shared" si="2"/>
         <v>46335</v>
       </c>
-      <c r="D25" s="51"/>
+      <c r="D25" s="38"/>
       <c r="E25" s="6" t="s">
         <v>23</v>
       </c>
@@ -1629,7 +1629,7 @@
       <c r="G25" s="13"/>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="45">
+      <c r="A26" s="50">
         <f>A24+1</f>
         <v>11</v>
       </c>
@@ -1639,15 +1639,15 @@
       <c r="C26" s="15">
         <v>46337</v>
       </c>
-      <c r="D26" s="48" t="s">
+      <c r="D26" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="50"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="55"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="46"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="17" t="str">
         <f>B24</f>
         <v>Thu</v>
@@ -1656,7 +1656,7 @@
         <f>C24+7</f>
         <v>46338</v>
       </c>
-      <c r="D27" s="51" t="s">
+      <c r="D27" s="38" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="6" t="s">
@@ -1670,7 +1670,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="47"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="17" t="str">
         <f>B25</f>
         <v>Mon</v>
@@ -1679,7 +1679,7 @@
         <f>C25+7</f>
         <v>46342</v>
       </c>
-      <c r="D28" s="51"/>
+      <c r="D28" s="38"/>
       <c r="E28" s="6" t="s">
         <v>25</v>
       </c>
@@ -1699,7 +1699,7 @@
         <f t="shared" si="2"/>
         <v>46345</v>
       </c>
-      <c r="D29" s="51" t="s">
+      <c r="D29" s="38" t="s">
         <v>76</v>
       </c>
       <c r="E29" s="6" t="s">
@@ -1720,7 +1720,7 @@
         <f t="shared" si="2"/>
         <v>46349</v>
       </c>
-      <c r="D30" s="51"/>
+      <c r="D30" s="38"/>
       <c r="E30" s="6" t="s">
         <v>27</v>
       </c>
@@ -1801,7 +1801,7 @@
         <f t="shared" si="2"/>
         <v>46363</v>
       </c>
-      <c r="D34" s="51" t="s">
+      <c r="D34" s="38" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="6" t="s">
@@ -1822,7 +1822,7 @@
         <f t="shared" si="2"/>
         <v>46366</v>
       </c>
-      <c r="D35" s="51"/>
+      <c r="D35" s="38"/>
       <c r="E35" s="6" t="s">
         <v>31</v>
       </c>
@@ -1856,6 +1856,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="D26:G26"/>
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="D34:D35"/>
     <mergeCell ref="D8:D9"/>
@@ -1868,11 +1873,6 @@
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="D20:G20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="D26:G26"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/math121-schedule.xlsx
+++ b/math121-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmac\git\math121-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D283FBB8-6F3F-4D34-9BDC-FF395464BAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F7B73B-8775-4AC1-8906-123FB5A0BF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="88">
   <si>
     <t>Class number</t>
   </si>
@@ -234,9 +234,6 @@
   </si>
   <si>
     <t>ch2</t>
-  </si>
-  <si>
-    <t>ch4</t>
   </si>
   <si>
     <t>ch5</t>
@@ -369,6 +366,36 @@
         <scheme val="minor"/>
       </rPr>
       <t>pp94-108</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ch4, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pp109-133</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ch4, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pp134-145</t>
     </r>
   </si>
 </sst>
@@ -742,6 +769,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -755,45 +821,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1117,7 +1144,7 @@
     <col min="4" max="4" width="36" style="36" customWidth="1"/>
     <col min="5" max="5" width="7.5703125" style="33" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" style="33" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" style="35" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" style="35" customWidth="1"/>
     <col min="8" max="8" width="37.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1138,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>39</v>
@@ -1155,7 +1182,7 @@
       <c r="C2" s="15">
         <v>46265</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="51" t="s">
         <v>46</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -1173,7 +1200,7 @@
         <f>C2+3</f>
         <v>46268</v>
       </c>
-      <c r="D3" s="38"/>
+      <c r="D3" s="51"/>
       <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
@@ -1242,7 +1269,7 @@
         <f t="shared" ref="C6:C35" si="2">C4+7</f>
         <v>46279</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="51" t="s">
         <v>49</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -1252,7 +1279,7 @@
         <v>57</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1265,13 +1292,13 @@
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="D7" s="38"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1287,7 +1314,7 @@
         <f t="shared" si="2"/>
         <v>46286</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="51" t="s">
         <v>50</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -1297,7 +1324,7 @@
         <v>58</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1310,12 +1337,14 @@
         <f t="shared" si="2"/>
         <v>46289</v>
       </c>
-      <c r="D9" s="38"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="9"/>
-      <c r="G9" s="21"/>
+      <c r="G9" s="13" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
@@ -1344,17 +1373,17 @@
     <row r="11" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" s="15">
         <v>46294</v>
       </c>
-      <c r="D11" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
+      <c r="D11" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
@@ -1388,7 +1417,7 @@
         <f>C10+7</f>
         <v>46300</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="51" t="s">
         <v>51</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -1396,7 +1425,7 @@
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1409,7 +1438,7 @@
         <f t="shared" si="2"/>
         <v>46303</v>
       </c>
-      <c r="D14" s="38"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="6" t="s">
         <v>15</v>
       </c>
@@ -1429,7 +1458,7 @@
         <f t="shared" si="2"/>
         <v>46307</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="51" t="s">
         <v>52</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -1439,7 +1468,7 @@
         <v>60</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1452,7 +1481,7 @@
         <f t="shared" si="2"/>
         <v>46310</v>
       </c>
-      <c r="D16" s="38"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="6" t="s">
         <v>17</v>
       </c>
@@ -1488,7 +1517,7 @@
         <f t="shared" si="2"/>
         <v>46317</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="51" t="s">
         <v>53</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -1498,7 +1527,7 @@
         <v>61</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1511,7 +1540,7 @@
         <f t="shared" si="2"/>
         <v>46321</v>
       </c>
-      <c r="D19" s="38"/>
+      <c r="D19" s="51"/>
       <c r="E19" s="6" t="s">
         <v>19</v>
       </c>
@@ -1521,28 +1550,28 @@
     <row r="20" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" s="15">
         <v>46322</v>
       </c>
-      <c r="D20" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="42"/>
+      <c r="D20" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="55"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <f>A18+1</f>
         <v>9</v>
       </c>
-      <c r="B21" s="43" t="str">
+      <c r="B21" s="38" t="str">
         <f>B18</f>
         <v>Thu</v>
       </c>
-      <c r="C21" s="45">
+      <c r="C21" s="40">
         <f>C18+7</f>
         <v>46324</v>
       </c>
@@ -1559,14 +1588,14 @@
     </row>
     <row r="22" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="49"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="44"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
@@ -1600,7 +1629,7 @@
         <f>C21+7</f>
         <v>46331</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="51" t="s">
         <v>54</v>
       </c>
       <c r="E24" s="6" t="s">
@@ -1608,7 +1637,7 @@
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1621,7 +1650,7 @@
         <f t="shared" si="2"/>
         <v>46335</v>
       </c>
-      <c r="D25" s="38"/>
+      <c r="D25" s="51"/>
       <c r="E25" s="6" t="s">
         <v>23</v>
       </c>
@@ -1629,25 +1658,25 @@
       <c r="G25" s="13"/>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="50">
+      <c r="A26" s="45">
         <f>A24+1</f>
         <v>11</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C26" s="15">
         <v>46337</v>
       </c>
-      <c r="D26" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="55"/>
+      <c r="D26" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="50"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="51"/>
+      <c r="A27" s="46"/>
       <c r="B27" s="17" t="str">
         <f>B24</f>
         <v>Thu</v>
@@ -1656,7 +1685,7 @@
         <f>C24+7</f>
         <v>46338</v>
       </c>
-      <c r="D27" s="38" t="s">
+      <c r="D27" s="51" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="6" t="s">
@@ -1666,11 +1695,11 @@
         <v>63</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="52"/>
+      <c r="A28" s="47"/>
       <c r="B28" s="17" t="str">
         <f>B25</f>
         <v>Mon</v>
@@ -1679,7 +1708,7 @@
         <f>C25+7</f>
         <v>46342</v>
       </c>
-      <c r="D28" s="38"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="6" t="s">
         <v>25</v>
       </c>
@@ -1699,15 +1728,15 @@
         <f t="shared" si="2"/>
         <v>46345</v>
       </c>
-      <c r="D29" s="38" t="s">
-        <v>76</v>
+      <c r="D29" s="51" t="s">
+        <v>75</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1720,7 +1749,7 @@
         <f t="shared" si="2"/>
         <v>46349</v>
       </c>
-      <c r="D30" s="38"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="6" t="s">
         <v>27</v>
       </c>
@@ -1801,14 +1830,14 @@
         <f t="shared" si="2"/>
         <v>46363</v>
       </c>
-      <c r="D34" s="38" t="s">
+      <c r="D34" s="51" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>30</v>
       </c>
       <c r="F34" s="32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G34" s="8"/>
     </row>
@@ -1822,7 +1851,7 @@
         <f t="shared" si="2"/>
         <v>46366</v>
       </c>
-      <c r="D35" s="38"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="6" t="s">
         <v>31</v>
       </c>
@@ -1846,7 +1875,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="37"/>
@@ -1856,11 +1885,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="D26:G26"/>
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="D34:D35"/>
     <mergeCell ref="D8:D9"/>
@@ -1873,6 +1897,11 @@
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="D26:G26"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/math121-schedule.xlsx
+++ b/math121-schedule.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F7B73B-8775-4AC1-8906-123FB5A0BF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>

--- a/math121-schedule.xlsx
+++ b/math121-schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmac\git\math121-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F7B73B-8775-4AC1-8906-123FB5A0BF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4665A1-9C1D-4B84-A312-EB9B22F4FEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="94">
   <si>
     <t>Class number</t>
   </si>
@@ -234,36 +234,6 @@
   </si>
   <si>
     <t>ch2</t>
-  </si>
-  <si>
-    <t>ch5</t>
-  </si>
-  <si>
-    <t>ch6</t>
-  </si>
-  <si>
-    <t>ch7</t>
-  </si>
-  <si>
-    <t>ch8</t>
-  </si>
-  <si>
-    <t>ch9</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ch10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(optional)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -336,9 +306,6 @@
     </r>
   </si>
   <si>
-    <t>updated 9/13/2026</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">ch3, </t>
     </r>
@@ -397,6 +364,111 @@
       </rPr>
       <t>pp134-145</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ch5, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pp146-157</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ch5, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pp157-170</t>
+    </r>
+  </si>
+  <si>
+    <t>ch6, pp171-182</t>
+  </si>
+  <si>
+    <t>ch6, pp183-197</t>
+  </si>
+  <si>
+    <t>ch7, pp198-211</t>
+  </si>
+  <si>
+    <t>ch7, pp212-223</t>
+  </si>
+  <si>
+    <t>ch8, pp224-235</t>
+  </si>
+  <si>
+    <t>ch8, pp236-248</t>
+  </si>
+  <si>
+    <t>ch9, pp249-263</t>
+  </si>
+  <si>
+    <t>ch9, pp263-279</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ch10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(optional)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pp280-285</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ch10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(optional)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pp286-288</t>
+    </r>
+  </si>
+  <si>
+    <t>updated 10/4/2026</t>
   </si>
 </sst>
 </file>
@@ -769,6 +841,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -806,21 +893,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1136,19 +1208,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="33" customWidth="1"/>
-    <col min="2" max="2" width="5.140625" style="34" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" style="35" customWidth="1"/>
+    <col min="1" max="1" width="6.1796875" style="33" customWidth="1"/>
+    <col min="2" max="2" width="5.1796875" style="34" customWidth="1"/>
+    <col min="3" max="3" width="6.453125" style="35" customWidth="1"/>
     <col min="4" max="4" width="36" style="36" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" style="33" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="33" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" style="35" customWidth="1"/>
-    <col min="8" max="8" width="37.85546875" customWidth="1"/>
+    <col min="5" max="5" width="7.54296875" style="33" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" style="33" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" style="35" customWidth="1"/>
+    <col min="8" max="8" width="37.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="7" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>32</v>
       </c>
@@ -1165,14 +1237,14 @@
         <v>0</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>39</v>
       </c>
       <c r="H1"/>
     </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -1182,7 +1254,7 @@
       <c r="C2" s="15">
         <v>46265</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="38" t="s">
         <v>46</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -1191,7 +1263,7 @@
       <c r="F2" s="9"/>
       <c r="G2" s="12"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="9"/>
       <c r="B3" s="17" t="s">
         <v>41</v>
@@ -1200,7 +1272,7 @@
         <f>C2+3</f>
         <v>46268</v>
       </c>
-      <c r="D3" s="51"/>
+      <c r="D3" s="38"/>
       <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
@@ -1209,7 +1281,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <f>A2+1</f>
         <v>2</v>
@@ -1235,7 +1307,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9"/>
       <c r="B5" s="17" t="str">
         <f>B3</f>
@@ -1256,7 +1328,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <f t="shared" ref="A6" si="0">A4+1</f>
         <v>3</v>
@@ -1269,7 +1341,7 @@
         <f t="shared" ref="C6:C35" si="2">C4+7</f>
         <v>46279</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="38" t="s">
         <v>49</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -1279,10 +1351,10 @@
         <v>57</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="9"/>
       <c r="B7" s="17" t="str">
         <f t="shared" si="1"/>
@@ -1292,16 +1364,16 @@
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="D7" s="51"/>
+      <c r="D7" s="38"/>
       <c r="E7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <f t="shared" ref="A8" si="3">A6+1</f>
         <v>4</v>
@@ -1314,7 +1386,7 @@
         <f t="shared" si="2"/>
         <v>46286</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="38" t="s">
         <v>50</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -1324,10 +1396,10 @@
         <v>58</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="9"/>
       <c r="B9" s="17" t="str">
         <f t="shared" si="1"/>
@@ -1337,16 +1409,16 @@
         <f t="shared" si="2"/>
         <v>46289</v>
       </c>
-      <c r="D9" s="51"/>
+      <c r="D9" s="38"/>
       <c r="E9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <f t="shared" ref="A10" si="4">A8+1</f>
         <v>5</v>
@@ -1370,22 +1442,22 @@
       </c>
       <c r="G10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9"/>
       <c r="B11" s="17" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C11" s="15">
         <v>46294</v>
       </c>
-      <c r="D11" s="52" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D11" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="9"/>
       <c r="B12" s="17" t="str">
         <f>B9</f>
@@ -1404,7 +1476,7 @@
       <c r="F12" s="9"/>
       <c r="G12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <f t="shared" ref="A13" si="5">A10+1</f>
         <v>6</v>
@@ -1417,7 +1489,7 @@
         <f>C10+7</f>
         <v>46300</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="38" t="s">
         <v>51</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -1425,10 +1497,10 @@
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
       <c r="B14" s="17" t="str">
         <f t="shared" si="1"/>
@@ -1438,14 +1510,16 @@
         <f t="shared" si="2"/>
         <v>46303</v>
       </c>
-      <c r="D14" s="51"/>
+      <c r="D14" s="38"/>
       <c r="E14" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="9"/>
-      <c r="G14" s="12"/>
-    </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G14" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <f t="shared" ref="A15" si="6">A13+1</f>
         <v>7</v>
@@ -1458,7 +1532,7 @@
         <f t="shared" si="2"/>
         <v>46307</v>
       </c>
-      <c r="D15" s="51" t="s">
+      <c r="D15" s="38" t="s">
         <v>52</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -1468,10 +1542,10 @@
         <v>60</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
       <c r="B16" s="17" t="str">
         <f t="shared" si="1"/>
@@ -1481,14 +1555,16 @@
         <f t="shared" si="2"/>
         <v>46310</v>
       </c>
-      <c r="D16" s="51"/>
+      <c r="D16" s="38"/>
       <c r="E16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F16" s="9"/>
-      <c r="G16" s="12"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G16" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="9"/>
       <c r="B17" s="17" t="str">
         <f t="shared" si="1"/>
@@ -1505,7 +1581,7 @@
       <c r="F17" s="22"/>
       <c r="G17" s="14"/>
     </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>8</v>
       </c>
@@ -1517,7 +1593,7 @@
         <f t="shared" si="2"/>
         <v>46317</v>
       </c>
-      <c r="D18" s="51" t="s">
+      <c r="D18" s="38" t="s">
         <v>53</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -1527,10 +1603,10 @@
         <v>61</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="9"/>
       <c r="B19" s="17" t="str">
         <f t="shared" si="1"/>
@@ -1540,38 +1616,40 @@
         <f t="shared" si="2"/>
         <v>46321</v>
       </c>
-      <c r="D19" s="51"/>
+      <c r="D19" s="38"/>
       <c r="E19" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F19" s="9"/>
-      <c r="G19" s="13"/>
-    </row>
-    <row r="20" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G19" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="B20" s="17" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C20" s="15">
         <v>46322</v>
       </c>
-      <c r="D20" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="55"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D20" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="42"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="9">
         <f>A18+1</f>
         <v>9</v>
       </c>
-      <c r="B21" s="38" t="str">
+      <c r="B21" s="43" t="str">
         <f>B18</f>
         <v>Thu</v>
       </c>
-      <c r="C21" s="40">
+      <c r="C21" s="45">
         <f>C18+7</f>
         <v>46324</v>
       </c>
@@ -1586,18 +1664,18 @@
       </c>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="42" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="44"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="44"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="9"/>
       <c r="B23" s="17" t="str">
         <f>B19</f>
@@ -1616,7 +1694,7 @@
       <c r="F23" s="26"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <f t="shared" ref="A24" si="7">A21+1</f>
         <v>10</v>
@@ -1629,7 +1707,7 @@
         <f>C21+7</f>
         <v>46331</v>
       </c>
-      <c r="D24" s="51" t="s">
+      <c r="D24" s="38" t="s">
         <v>54</v>
       </c>
       <c r="E24" s="6" t="s">
@@ -1637,10 +1715,10 @@
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9"/>
       <c r="B25" s="17" t="str">
         <f t="shared" si="1"/>
@@ -1650,33 +1728,35 @@
         <f t="shared" si="2"/>
         <v>46335</v>
       </c>
-      <c r="D25" s="51"/>
+      <c r="D25" s="38"/>
       <c r="E25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F25" s="9"/>
-      <c r="G25" s="13"/>
-    </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="45">
+      <c r="G25" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="50">
         <f>A24+1</f>
         <v>11</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C26" s="15">
         <v>46337</v>
       </c>
-      <c r="D26" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="50"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="46"/>
+      <c r="D26" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="55"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="51"/>
       <c r="B27" s="17" t="str">
         <f>B24</f>
         <v>Thu</v>
@@ -1685,7 +1765,7 @@
         <f>C24+7</f>
         <v>46338</v>
       </c>
-      <c r="D27" s="51" t="s">
+      <c r="D27" s="38" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="6" t="s">
@@ -1695,11 +1775,11 @@
         <v>63</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="47"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="52"/>
       <c r="B28" s="17" t="str">
         <f>B25</f>
         <v>Mon</v>
@@ -1708,14 +1788,16 @@
         <f>C25+7</f>
         <v>46342</v>
       </c>
-      <c r="D28" s="51"/>
+      <c r="D28" s="38"/>
       <c r="E28" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F28" s="23"/>
-      <c r="G28" s="12"/>
-    </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G28" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <f>A26+1</f>
         <v>12</v>
@@ -1728,18 +1810,18 @@
         <f t="shared" si="2"/>
         <v>46345</v>
       </c>
-      <c r="D29" s="51" t="s">
-        <v>75</v>
+      <c r="D29" s="38" t="s">
+        <v>69</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="B30" s="17" t="str">
         <f t="shared" si="1"/>
@@ -1749,16 +1831,18 @@
         <f t="shared" si="2"/>
         <v>46349</v>
       </c>
-      <c r="D30" s="51"/>
+      <c r="D30" s="38"/>
       <c r="E30" s="6" t="s">
         <v>27</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G30" s="13"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G30" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
       <c r="B31" s="17" t="str">
         <f t="shared" si="1"/>
@@ -1775,7 +1859,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="12"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="9">
         <f>A29+1</f>
         <v>13</v>
@@ -1797,7 +1881,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="8"/>
     </row>
-    <row r="33" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="19"/>
       <c r="B33" s="18" t="str">
         <f t="shared" si="1"/>
@@ -1817,7 +1901,7 @@
       <c r="G33" s="8"/>
       <c r="H33"/>
     </row>
-    <row r="34" spans="1:8" ht="27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A34" s="9">
         <f t="shared" ref="A34" si="8">A32+1</f>
         <v>14</v>
@@ -1830,18 +1914,18 @@
         <f t="shared" si="2"/>
         <v>46363</v>
       </c>
-      <c r="D34" s="51" t="s">
+      <c r="D34" s="38" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>30</v>
       </c>
       <c r="F34" s="32" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="9"/>
       <c r="B35" s="17" t="str">
         <f t="shared" si="1"/>
@@ -1851,14 +1935,14 @@
         <f t="shared" si="2"/>
         <v>46366</v>
       </c>
-      <c r="D35" s="51"/>
+      <c r="D35" s="38"/>
       <c r="E35" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="39" x14ac:dyDescent="0.35">
       <c r="A36" s="9"/>
       <c r="B36" s="17" t="s">
         <v>35</v>
@@ -1873,18 +1957,23 @@
       <c r="F36" s="9"/>
       <c r="G36" s="12"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="35" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="37"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D39"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="D26:G26"/>
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="D34:D35"/>
     <mergeCell ref="D8:D9"/>
@@ -1897,11 +1986,6 @@
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="D20:G20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="D26:G26"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
